--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienNghiViec.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienNghiViec.xlsx
@@ -1,35 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2. HR\HR_SS\HR_S&amp;K\SK2025\Debug\Teamleate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739FD396-6A75-4E9F-A973-5F59657FFF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6510"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>SNK</author>
   </authors>
   <commentList>
-    <comment ref="Y6" authorId="0" shapeId="0">
+    <comment ref="Y6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -53,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD6" authorId="0" shapeId="0">
+    <comment ref="AD6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -328,9 +340,6 @@
     <t>Factory_ID</t>
   </si>
   <si>
-    <t>Position_ID</t>
-  </si>
-  <si>
     <t>BankAccount</t>
   </si>
   <si>
@@ -355,18 +364,9 @@
     <t>TinhTrangNV</t>
   </si>
   <si>
-    <t>DepCode</t>
-  </si>
-  <si>
-    <t>PositionCategory_ID</t>
-  </si>
-  <si>
     <t>TonGiao</t>
   </si>
   <si>
-    <t>DanToc</t>
-  </si>
-  <si>
     <t>SoNha_ThuongTru</t>
   </si>
   <si>
@@ -404,14 +404,26 @@
   </si>
   <si>
     <t>EMPLOYEE LIST - DANH SÁCH NHÂN VIÊN NGHỈ VIỆC</t>
+  </si>
+  <si>
+    <t>DepartmentName</t>
+  </si>
+  <si>
+    <t>SectionName</t>
+  </si>
+  <si>
+    <t>ChucDanhName</t>
+  </si>
+  <si>
+    <t>Nation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -463,16 +475,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -545,31 +556,30 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -578,6 +588,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -858,7 +869,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -906,177 +917,331 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="F2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="F3" s="11" t="str">
+      <c r="F3" s="10" t="str">
         <f>"Từ ngày " &amp; A1 &amp;" đến ngày "&amp;A2</f>
         <v>Từ ngày 1 đến ngày 2</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
-    <row r="4" spans="1:52" s="5" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:52" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+    <row r="4" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="11">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11">
+        <v>2</v>
+      </c>
+      <c r="D4" s="11">
+        <v>2</v>
+      </c>
+      <c r="E4" s="11">
+        <v>2</v>
+      </c>
+      <c r="F4" s="11">
+        <v>2</v>
+      </c>
+      <c r="G4" s="11">
+        <v>2</v>
+      </c>
+      <c r="H4" s="11">
+        <v>2</v>
+      </c>
+      <c r="I4" s="11">
+        <v>2</v>
+      </c>
+      <c r="J4" s="11">
+        <v>2</v>
+      </c>
+      <c r="K4" s="11">
+        <v>2</v>
+      </c>
+      <c r="L4" s="11">
+        <v>2</v>
+      </c>
+      <c r="M4" s="11">
+        <v>2</v>
+      </c>
+      <c r="N4" s="11">
+        <v>2</v>
+      </c>
+      <c r="O4" s="11">
+        <v>2</v>
+      </c>
+      <c r="P4" s="11">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>2</v>
+      </c>
+      <c r="R4" s="11">
+        <v>2</v>
+      </c>
+      <c r="S4" s="11">
+        <v>2</v>
+      </c>
+      <c r="T4" s="11">
+        <v>2</v>
+      </c>
+      <c r="U4" s="11">
+        <v>2</v>
+      </c>
+      <c r="V4" s="11">
+        <v>2</v>
+      </c>
+      <c r="W4" s="11">
+        <v>2</v>
+      </c>
+      <c r="X4" s="11">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="11">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AI4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AO4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AP4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AQ4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AR4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AT4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AV4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AX4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="T5" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V5" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="X5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB5" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AC5" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH5" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="AI5" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ5" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="W5" s="5" t="s">
+      <c r="AK5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="X5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y5" s="5" t="s">
+      <c r="AL5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN5" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ5" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR5" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="AT5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AU5" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="Z5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AF5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH5" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI5" s="5" t="s">
+      <c r="AV5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW5" s="11" t="s">
         <v>85</v>
-      </c>
-      <c r="AJ5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN5" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AO5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ5" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AR5" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="AS5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="AT5" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AV5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AW5" s="5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:52" ht="42" x14ac:dyDescent="0.25">
@@ -1235,57 +1400,57 @@
       </c>
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="7"/>
-      <c r="AK7" s="6"/>
-      <c r="AL7" s="8"/>
-      <c r="AM7" s="8"/>
-      <c r="AN7" s="8"/>
-      <c r="AO7" s="8"/>
-      <c r="AP7" s="8"/>
-      <c r="AQ7" s="8"/>
-      <c r="AR7" s="8"/>
-      <c r="AS7" s="8"/>
-      <c r="AT7" s="8"/>
-      <c r="AU7" s="8"/>
-      <c r="AV7" s="8"/>
-      <c r="AW7" s="8"/>
-      <c r="AX7" s="8"/>
-      <c r="AY7" s="8"/>
-      <c r="AZ7" s="8"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="5"/>
+      <c r="AF7" s="5"/>
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="5"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
+      <c r="AO7" s="7"/>
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="7"/>
+      <c r="AR7" s="7"/>
+      <c r="AS7" s="7"/>
+      <c r="AT7" s="7"/>
+      <c r="AU7" s="7"/>
+      <c r="AV7" s="7"/>
+      <c r="AW7" s="7"/>
+      <c r="AX7" s="7"/>
+      <c r="AY7" s="7"/>
+      <c r="AZ7" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienNghiViec.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienNghiViec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739FD396-6A75-4E9F-A973-5F59657FFF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFFA03B-68E2-4B3F-A054-7BD59AE7118A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
   <si>
     <t>STT
 No.</t>
@@ -325,21 +325,9 @@
     <t>Address_Permanent</t>
   </si>
   <si>
-    <t>Tinh_TP_ThuongTru</t>
-  </si>
-  <si>
-    <t>Huyen_ThiXa_ThuongTru</t>
-  </si>
-  <si>
-    <t>Xa_Phuong_ThuongTru</t>
-  </si>
-  <si>
     <t>NativePlace</t>
   </si>
   <si>
-    <t>Factory_ID</t>
-  </si>
-  <si>
     <t>BankAccount</t>
   </si>
   <si>
@@ -367,9 +355,6 @@
     <t>TonGiao</t>
   </si>
   <si>
-    <t>SoNha_ThuongTru</t>
-  </si>
-  <si>
     <t>TernimationDate</t>
   </si>
   <si>
@@ -416,6 +401,9 @@
   </si>
   <si>
     <t>Nation</t>
+  </si>
+  <si>
+    <t>FactoryName</t>
   </si>
 </sst>
 </file>
@@ -582,13 +570,13 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -917,331 +905,331 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="F2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="F3" s="10" t="str">
+      <c r="F3" s="11" t="str">
         <f>"Từ ngày " &amp; A1 &amp;" đến ngày "&amp;A2</f>
         <v>Từ ngày 1 đến ngày 2</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
-        <v>2</v>
-      </c>
-      <c r="C4" s="11">
-        <v>2</v>
-      </c>
-      <c r="D4" s="11">
-        <v>2</v>
-      </c>
-      <c r="E4" s="11">
-        <v>2</v>
-      </c>
-      <c r="F4" s="11">
-        <v>2</v>
-      </c>
-      <c r="G4" s="11">
-        <v>2</v>
-      </c>
-      <c r="H4" s="11">
-        <v>2</v>
-      </c>
-      <c r="I4" s="11">
-        <v>2</v>
-      </c>
-      <c r="J4" s="11">
-        <v>2</v>
-      </c>
-      <c r="K4" s="11">
-        <v>2</v>
-      </c>
-      <c r="L4" s="11">
-        <v>2</v>
-      </c>
-      <c r="M4" s="11">
-        <v>2</v>
-      </c>
-      <c r="N4" s="11">
-        <v>2</v>
-      </c>
-      <c r="O4" s="11">
-        <v>2</v>
-      </c>
-      <c r="P4" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>2</v>
-      </c>
-      <c r="R4" s="11">
-        <v>2</v>
-      </c>
-      <c r="S4" s="11">
-        <v>2</v>
-      </c>
-      <c r="T4" s="11">
-        <v>2</v>
-      </c>
-      <c r="U4" s="11">
-        <v>2</v>
-      </c>
-      <c r="V4" s="11">
-        <v>2</v>
-      </c>
-      <c r="W4" s="11">
-        <v>2</v>
-      </c>
-      <c r="X4" s="11">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="11">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AD4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AE4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AF4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AG4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AH4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AI4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AJ4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AK4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AL4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AM4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AN4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AO4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AP4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AQ4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AR4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AS4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AT4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AU4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AV4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AW4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AX4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AY4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AZ4" s="11">
+    <row r="4" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="9">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9">
+        <v>2</v>
+      </c>
+      <c r="L4" s="9">
+        <v>2</v>
+      </c>
+      <c r="M4" s="9">
+        <v>2</v>
+      </c>
+      <c r="N4" s="9">
+        <v>2</v>
+      </c>
+      <c r="O4" s="9">
+        <v>2</v>
+      </c>
+      <c r="P4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>2</v>
+      </c>
+      <c r="R4" s="9">
+        <v>2</v>
+      </c>
+      <c r="S4" s="9">
+        <v>2</v>
+      </c>
+      <c r="T4" s="9">
+        <v>2</v>
+      </c>
+      <c r="U4" s="9">
+        <v>2</v>
+      </c>
+      <c r="V4" s="9">
+        <v>2</v>
+      </c>
+      <c r="W4" s="9">
+        <v>2</v>
+      </c>
+      <c r="X4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AO4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AP4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AQ4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AR4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AT4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AV4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AX4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
+    <row r="5" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="L5" s="11" t="s">
+      <c r="AJ5" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" s="11" t="s">
+      <c r="AK5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AR5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS5" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="W5" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="X5" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y5" s="11" t="s">
+      <c r="AV5" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="Z5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB5" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH5" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ5" s="11" t="s">
+      <c r="AW5" s="9" t="s">
         <v>80</v>
-      </c>
-      <c r="AK5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN5" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="AO5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR5" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AS5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AT5" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AU5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AV5" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW5" s="11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:52" ht="42" x14ac:dyDescent="0.25">

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienNghiViec.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienNghiViec.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFFA03B-68E2-4B3F-A054-7BD59AE7118A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84A963D-66CE-45A5-A901-A00F4EF031D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -576,6 +576,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -893,13 +899,16 @@
     <col min="32" max="32" width="18" customWidth="1"/>
     <col min="33" max="33" width="17.7109375" customWidth="1"/>
     <col min="34" max="34" width="12.5703125" customWidth="1"/>
-    <col min="35" max="37" width="17.85546875" customWidth="1"/>
+    <col min="35" max="35" width="17.85546875" customWidth="1"/>
+    <col min="36" max="36" width="17.85546875" style="12" customWidth="1"/>
+    <col min="37" max="37" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1">
         <v>1</v>
       </c>
+      <c r="AJ1" s="13"/>
     </row>
     <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2">
@@ -916,6 +925,7 @@
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
+      <c r="AJ2" s="13"/>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="F3" s="11" t="str">
@@ -930,6 +940,7 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
+      <c r="AJ3" s="13"/>
     </row>
     <row r="4" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="9">
@@ -1034,7 +1045,7 @@
       <c r="AI4" s="9">
         <v>2</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AJ4" s="14">
         <v>2</v>
       </c>
       <c r="AK4" s="9">
@@ -1189,7 +1200,7 @@
       <c r="AI5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="AJ5" s="9" t="s">
+      <c r="AJ5" s="14" t="s">
         <v>75</v>
       </c>
       <c r="AK5" s="9" t="s">
@@ -1335,7 +1346,7 @@
       <c r="AI6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ6" s="1" t="s">
+      <c r="AJ6" s="15" t="s">
         <v>34</v>
       </c>
       <c r="AK6" s="1" t="s">
